--- a/data/vendor_map.xlsx
+++ b/data/vendor_map.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\rygarcorp.com\shares\Cornerstone\Garretts Reports\Sales Report App\Excell Sheets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E205AF3-F902-454E-83FB-9E2B870BB554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A39D4995-03BB-4DBC-AD00-6E7DF2FB8F74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="77040" windowHeight="21390" xr2:uid="{5542AD97-7A4C-4C40-ABF5-82E45C8FC76F}"/>
+    <workbookView xWindow="76680" yWindow="-825" windowWidth="29040" windowHeight="15990" xr2:uid="{5542AD97-7A4C-4C40-ABF5-82E45C8FC76F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1746" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1698" uniqueCount="295">
   <si>
     <t>BGC10</t>
   </si>
@@ -906,43 +906,10 @@
     <t>Ovala-42</t>
   </si>
   <si>
+    <t>Orgil</t>
+  </si>
+  <si>
     <t>ACE Hardware</t>
-  </si>
-  <si>
-    <t>Lotus Light</t>
-  </si>
-  <si>
-    <t>Olla</t>
-  </si>
-  <si>
-    <t>.25oz lip tube</t>
-  </si>
-  <si>
-    <t>2 oz</t>
-  </si>
-  <si>
-    <t>5 oz</t>
-  </si>
-  <si>
-    <t>Multi Purpose 3 oz</t>
-  </si>
-  <si>
-    <t>Calming 3 oz</t>
-  </si>
-  <si>
-    <t>Beautifying Mud 3oz</t>
-  </si>
-  <si>
-    <t>Clarifying Mud 3 oz</t>
-  </si>
-  <si>
-    <t>Detoxifying Mud 3 oz</t>
-  </si>
-  <si>
-    <t>Waxelene</t>
-  </si>
-  <si>
-    <t>Orgill</t>
   </si>
 </sst>
 </file>
@@ -1340,7 +1307,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6055176-08B8-4018-B9DF-7F26AB5DB49D}">
-  <dimension ref="A1:K635"/>
+  <dimension ref="A1:K614"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
@@ -9538,7 +9505,7 @@
     </row>
     <row r="607" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="B607" s="3" t="s">
         <v>22</v>
@@ -9552,7 +9519,7 @@
     </row>
     <row r="608" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="B608" s="3" t="s">
         <v>23</v>
@@ -9563,7 +9530,7 @@
     </row>
     <row r="609" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="B609" s="3">
         <v>4642</v>
@@ -9577,7 +9544,7 @@
     </row>
     <row r="610" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="B610" s="3">
         <v>6642</v>
@@ -9591,7 +9558,7 @@
     </row>
     <row r="613" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B613" s="3" t="s">
         <v>22</v>
@@ -9602,237 +9569,13 @@
     </row>
     <row r="614" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B614" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D614" t="s">
         <v>140</v>
-      </c>
-    </row>
-    <row r="618" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A618" t="s">
-        <v>294</v>
-      </c>
-      <c r="B618" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="C618" s="6">
-        <v>3.15</v>
-      </c>
-      <c r="D618" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="619" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A619" t="s">
-        <v>294</v>
-      </c>
-      <c r="B619" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="C619" s="6">
-        <v>7.65</v>
-      </c>
-      <c r="D619" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="620" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A620" t="s">
-        <v>294</v>
-      </c>
-      <c r="B620" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="C620" s="6">
-        <v>8.1</v>
-      </c>
-      <c r="D620" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="621" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A621" t="s">
-        <v>294</v>
-      </c>
-      <c r="B621" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="C621" s="6">
-        <v>10.8</v>
-      </c>
-      <c r="D621" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="622" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A622" t="s">
-        <v>294</v>
-      </c>
-      <c r="B622" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="C622" s="6">
-        <v>12.2</v>
-      </c>
-      <c r="D622" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="623" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A623" t="s">
-        <v>294</v>
-      </c>
-      <c r="B623" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="C623" s="6">
-        <v>11.25</v>
-      </c>
-      <c r="D623" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="624" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A624" t="s">
-        <v>294</v>
-      </c>
-      <c r="B624" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="C624" s="6">
-        <v>11.25</v>
-      </c>
-      <c r="D624" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="625" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A625" t="s">
-        <v>294</v>
-      </c>
-      <c r="B625" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="C625" s="6">
-        <v>11.25</v>
-      </c>
-      <c r="D625" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="628" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A628" t="s">
-        <v>295</v>
-      </c>
-      <c r="B628" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="C628" s="6">
-        <v>3.36</v>
-      </c>
-      <c r="D628" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="629" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A629" t="s">
-        <v>295</v>
-      </c>
-      <c r="B629" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="C629" s="6">
-        <v>10.19</v>
-      </c>
-      <c r="D629" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="630" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A630" t="s">
-        <v>295</v>
-      </c>
-      <c r="B630" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="C630" s="6">
-        <v>14.4</v>
-      </c>
-      <c r="D630" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="631" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A631" t="s">
-        <v>295</v>
-      </c>
-      <c r="B631" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="C631" s="6">
-        <v>14.39</v>
-      </c>
-      <c r="D631" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="632" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A632" t="s">
-        <v>295</v>
-      </c>
-      <c r="B632" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="C632" s="6">
-        <v>11.52</v>
-      </c>
-      <c r="D632" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="633" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A633" t="s">
-        <v>295</v>
-      </c>
-      <c r="B633" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="C633" s="6">
-        <v>12</v>
-      </c>
-      <c r="D633" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="634" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A634" t="s">
-        <v>295</v>
-      </c>
-      <c r="B634" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="C634" s="6">
-        <v>12</v>
-      </c>
-      <c r="D634" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="635" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A635" t="s">
-        <v>295</v>
-      </c>
-      <c r="B635" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="C635" s="6">
-        <v>12</v>
-      </c>
-      <c r="D635" t="s">
-        <v>304</v>
       </c>
     </row>
   </sheetData>
